--- a/Sample_run/1/student/HoangHHHE182296/OverallSummary.xlsx
+++ b/Sample_run/1/student/HoangHHHE182296/OverallSummary.xlsx
@@ -55,16 +55,13 @@
     <x:t>TC4</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 3 FAIL (ALL-OR-NOTHING), 8 PASS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TC5</x:t>
   </x:si>
   <x:si>
     <x:t>TC6</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 8 FAIL (ALL-OR-NOTHING), 14 PASS</x:t>
+    <x:t>Network flows: 2 FAIL (ALL-OR-NOTHING), 20 PASS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -513,21 +510,21 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -544,7 +541,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>10</x:v>
@@ -556,7 +553,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
